--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6D4570-63FA-4F13-8710-9EF8A344C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C7B1FF-DAC3-4500-891F-22A5474DDFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="1215">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3760,43 +3760,154 @@
     <t>Sahraoui khaled</t>
   </si>
   <si>
-    <t>cite 720 bt 17 n22</t>
-  </si>
-  <si>
     <t>NB(398/2026)</t>
   </si>
   <si>
     <t>Fergani abdenasser</t>
   </si>
   <si>
-    <t>cite 720 bt 04 n02</t>
-  </si>
-  <si>
     <t>NB(402/2026)</t>
   </si>
   <si>
     <t>Abidi mouni</t>
   </si>
   <si>
-    <t>cite 720 bt 08 n07</t>
-  </si>
-  <si>
     <t>NB(391/2026)</t>
   </si>
   <si>
     <t>Hassam ahmed</t>
   </si>
   <si>
-    <t>ain omrane</t>
-  </si>
-  <si>
     <t>NB(285/2026)</t>
   </si>
   <si>
     <t>Maizi samira</t>
   </si>
   <si>
-    <t>cite 720 bt 15 n32</t>
+    <t>Yebda hamid</t>
+  </si>
+  <si>
+    <t>Bounadri djamel</t>
+  </si>
+  <si>
+    <t>NB(092/2026)</t>
+  </si>
+  <si>
+    <t>Phar dahmani saadiya</t>
+  </si>
+  <si>
+    <t>NB(250/2026)</t>
+  </si>
+  <si>
+    <t>Karrache smail</t>
+  </si>
+  <si>
+    <t>NB(352/2026)</t>
+  </si>
+  <si>
+    <t>Benattalah med salah eddine</t>
+  </si>
+  <si>
+    <t>NB(404/2026)</t>
+  </si>
+  <si>
+    <t>Ibaliden boudjemaa</t>
+  </si>
+  <si>
+    <t>NB(390/2026)</t>
+  </si>
+  <si>
+    <t>Boucheraire hamid</t>
+  </si>
+  <si>
+    <t>NB(327/2026)</t>
+  </si>
+  <si>
+    <t>Mag bakhtaoui missoum</t>
+  </si>
+  <si>
+    <t>NB(677/2024)</t>
+  </si>
+  <si>
+    <t>NB(375/2026)</t>
+  </si>
+  <si>
+    <t>Harrag rabah</t>
+  </si>
+  <si>
+    <t>NB(411/2026)</t>
+  </si>
+  <si>
+    <t>B21169</t>
+  </si>
+  <si>
+    <t>NB(417/2026)</t>
+  </si>
+  <si>
+    <t>Korteby karima</t>
+  </si>
+  <si>
+    <t>reu emir aek</t>
+  </si>
+  <si>
+    <t>NB(188/2026)</t>
+  </si>
+  <si>
+    <t>Zouaoucha aek</t>
+  </si>
+  <si>
+    <t>Benmahieddine a/rahim</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 18 n 27</t>
+  </si>
+  <si>
+    <t>NB(369/2026)</t>
+  </si>
+  <si>
+    <t>Oueld benaissa azzedine</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 09 n 13</t>
+  </si>
+  <si>
+    <t>NB(430/2026)</t>
+  </si>
+  <si>
+    <t>Menadli wassila</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 11 n 01</t>
+  </si>
+  <si>
+    <t>NB(431/2026)</t>
+  </si>
+  <si>
+    <t>Hamrouche hadjira</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 19 n 11</t>
+  </si>
+  <si>
+    <t>NB(413/2026)</t>
+  </si>
+  <si>
+    <t>Boumekhlef rachid</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 13 n 27</t>
+  </si>
+  <si>
+    <t>NB(414/2026)</t>
+  </si>
+  <si>
+    <t>NB(286/2026)</t>
+  </si>
+  <si>
+    <t>Kermazli fethi</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 11 n 09</t>
   </si>
 </sst>
 </file>
@@ -26319,7 +26430,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -26341,7 +26452,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -26381,7 +26492,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -26418,24 +26529,26 @@
         <v>1</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1163</v>
+        <v>72</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>18</v>
+        <v>284</v>
       </c>
       <c r="D7" s="13">
-        <v>2026143453</v>
+        <v>2026004070</v>
       </c>
       <c r="E7" s="15">
         <v>46267</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>162</v>
+        <v>1171</v>
       </c>
       <c r="G7" s="17">
         <v>1</v>
       </c>
-      <c r="H7" s="18"/>
+      <c r="H7" s="4" t="s">
+        <v>1170</v>
+      </c>
       <c r="I7" s="20"/>
       <c r="J7" s="19"/>
       <c r="K7" s="4"/>
@@ -26446,29 +26559,25 @@
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>19</v>
+        <v>1163</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="13">
-        <v>2026143456</v>
+        <v>2026143453</v>
       </c>
       <c r="E8" s="15">
         <v>46267</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>1169</v>
+        <v>162</v>
       </c>
       <c r="G8" s="17">
         <v>1</v>
       </c>
-      <c r="H8" s="18" t="s">
-        <v>1167</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>1168</v>
-      </c>
+      <c r="H8" s="18"/>
+      <c r="I8" s="20"/>
       <c r="J8" s="20"/>
       <c r="K8" s="4"/>
     </row>
@@ -26484,23 +26593,21 @@
         <v>18</v>
       </c>
       <c r="D9" s="13">
-        <v>2026143457</v>
+        <v>2026143456</v>
       </c>
       <c r="E9" s="15">
         <v>46267</v>
       </c>
       <c r="F9" s="16" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>1166</v>
       </c>
-      <c r="G9" s="17">
-        <v>1</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>1164</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>1165</v>
-      </c>
+      <c r="I9" s="20"/>
       <c r="J9" s="20"/>
       <c r="K9" s="4"/>
     </row>
@@ -26516,23 +26623,21 @@
         <v>18</v>
       </c>
       <c r="D10" s="13">
-        <v>2026143458</v>
+        <v>2026143457</v>
       </c>
       <c r="E10" s="15">
         <v>46267</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
       <c r="G10" s="17">
         <v>1</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>1170</v>
-      </c>
-      <c r="I10" s="20" t="s">
-        <v>1171</v>
-      </c>
+        <v>1164</v>
+      </c>
+      <c r="I10" s="20"/>
       <c r="J10" s="20"/>
       <c r="K10" s="4"/>
     </row>
@@ -26542,29 +26647,27 @@
         <v>5</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="D11" s="13">
-        <v>2026004070</v>
+        <v>2026143458</v>
       </c>
       <c r="E11" s="15">
         <v>46267</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="G11" s="17">
         <v>1</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I11" s="20" t="s">
-        <v>1174</v>
-      </c>
+      <c r="H11" s="18" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="4"/>
     </row>
@@ -26583,20 +26686,18 @@
         <v>2026143459</v>
       </c>
       <c r="E12" s="15">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>791</v>
+        <v>1190</v>
       </c>
       <c r="G12" s="17">
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>1176</v>
-      </c>
-      <c r="I12" s="20" t="s">
-        <v>1177</v>
-      </c>
+        <v>1172</v>
+      </c>
+      <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="4"/>
     </row>
@@ -26605,15 +26706,27 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2026003592</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>1177</v>
+      </c>
       <c r="G13" s="17">
         <v>1</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="18" t="s">
+        <v>1176</v>
+      </c>
       <c r="I13" s="20"/>
       <c r="J13" s="20"/>
       <c r="K13" s="4"/>
@@ -26623,15 +26736,27 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
+      <c r="B14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2026003595</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>1179</v>
+      </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="18" t="s">
+        <v>1178</v>
+      </c>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
@@ -26641,15 +26766,27 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
+      <c r="B15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2026004026</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>1181</v>
+      </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
-      <c r="H15" s="18"/>
+      <c r="H15" s="18" t="s">
+        <v>1180</v>
+      </c>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
     </row>
@@ -26658,15 +26795,27 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="16"/>
+      <c r="B16" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2026004027</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>1183</v>
+      </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
-      <c r="H16" s="18"/>
+      <c r="H16" s="18" t="s">
+        <v>1182</v>
+      </c>
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
@@ -26675,15 +26824,27 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
+      <c r="B17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2026004096</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>1104</v>
+      </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
-      <c r="H17" s="18"/>
+      <c r="H17" s="4" t="s">
+        <v>1173</v>
+      </c>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
     </row>
@@ -26692,15 +26853,27 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
+      <c r="B18" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2026004100</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>1185</v>
+      </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
-      <c r="H18" s="18"/>
+      <c r="H18" s="18" t="s">
+        <v>1184</v>
+      </c>
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
     </row>
@@ -26709,15 +26882,27 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
+      <c r="B19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2026143431</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>1175</v>
+      </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
-      <c r="H19" s="18"/>
+      <c r="H19" s="18" t="s">
+        <v>1174</v>
+      </c>
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
     </row>
@@ -26726,15 +26911,27 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2026143460</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46274</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>1187</v>
+      </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
-      <c r="H20" s="18"/>
+      <c r="H20" s="18" t="s">
+        <v>1186</v>
+      </c>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
@@ -26743,15 +26940,27 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2026004099</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46277</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>1188</v>
+      </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
-      <c r="H21" s="18"/>
+      <c r="H21" s="18" t="s">
+        <v>1189</v>
+      </c>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
@@ -26760,16 +26969,30 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
+      <c r="B22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2026003593</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46278</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>1212</v>
+      </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="20"/>
+      <c r="H22" s="4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>1214</v>
+      </c>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26777,16 +27000,30 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
+      <c r="B23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2026144302</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46278</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>1211</v>
+      </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="20"/>
+      <c r="H23" s="18" t="s">
+        <v>1209</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>1210</v>
+      </c>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26794,16 +27031,30 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2026144305</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46278</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>1208</v>
+      </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="20"/>
+      <c r="H24" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>1207</v>
+      </c>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26811,16 +27062,30 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2026144310</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46278</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>1199</v>
+      </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="20"/>
+      <c r="H25" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>1198</v>
+      </c>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26828,16 +27093,30 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2026004097</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>1192</v>
+      </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="20"/>
+      <c r="H26" s="18" t="s">
+        <v>1193</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>1194</v>
+      </c>
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26845,16 +27124,30 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2026144303</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>1205</v>
+      </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="20"/>
+      <c r="H27" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>1204</v>
+      </c>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26862,16 +27155,30 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2026144304</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>1202</v>
+      </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="20"/>
+      <c r="H28" s="18" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>1201</v>
+      </c>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26879,16 +27186,30 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2026144306</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>1195</v>
+      </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="20"/>
+      <c r="H29" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>959</v>
+      </c>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26896,15 +27217,25 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="13" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2026144309</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H30" s="4"/>
+      <c r="H30" s="18"/>
       <c r="I30" s="20"/>
       <c r="J30" s="4"/>
     </row>
@@ -28282,9 +28613,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I11">
-    <sortCondition ref="C7:C11"/>
-    <sortCondition ref="D7:D11"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I30">
+    <sortCondition ref="E7:E30"/>
+    <sortCondition ref="D7:D30"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C7B1FF-DAC3-4500-891F-22A5474DDFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB8B6FA-CB46-4E6B-BE6E-1CE0477ABC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="1215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="1240">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3908,6 +3908,81 @@
   </si>
   <si>
     <t>cité 720 logts bt 11 n 09</t>
+  </si>
+  <si>
+    <t>NB(202/2025)</t>
+  </si>
+  <si>
+    <t>Khazaz med</t>
+  </si>
+  <si>
+    <t>djenane toubal n97</t>
+  </si>
+  <si>
+    <t>NB(339/2026)</t>
+  </si>
+  <si>
+    <t>Megatli el hadj</t>
+  </si>
+  <si>
+    <t>Hafrat lakhdar</t>
+  </si>
+  <si>
+    <t>NB(343/2025)</t>
+  </si>
+  <si>
+    <t>Lamri redha</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 14 n 11</t>
+  </si>
+  <si>
+    <t>NB(441/2026)</t>
+  </si>
+  <si>
+    <t>Chikaoui samir</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 12 n 24</t>
+  </si>
+  <si>
+    <t>NB(429/2026)</t>
+  </si>
+  <si>
+    <t>Aouf med</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 11 n 30</t>
+  </si>
+  <si>
+    <t>NB(436/2026)</t>
+  </si>
+  <si>
+    <t>Menai khaled</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 13 n 10</t>
+  </si>
+  <si>
+    <t>NB(462/2025)</t>
+  </si>
+  <si>
+    <t>Boualami smail</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 12 n 32</t>
+  </si>
+  <si>
+    <t>NB(432/2025)</t>
+  </si>
+  <si>
+    <t>Laref hamid</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 14 n 29</t>
+  </si>
+  <si>
+    <t>NB(425/2025)</t>
   </si>
 </sst>
 </file>
@@ -26452,7 +26527,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -26492,7 +26567,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -27244,16 +27319,30 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2026003594</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46281</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>1218</v>
+      </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="20"/>
+      <c r="H31" s="4" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>950</v>
+      </c>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27261,16 +27350,30 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="B32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2026003597</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46281</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>1221</v>
+      </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="20"/>
+      <c r="H32" s="18" t="s">
+        <v>1220</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>1157</v>
+      </c>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27278,16 +27381,30 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2026144301</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46281</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>1215</v>
+      </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="20"/>
+      <c r="H33" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>1217</v>
+      </c>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27295,16 +27412,30 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2026144307</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46281</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>1224</v>
+      </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="20"/>
+      <c r="H34" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>1223</v>
+      </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27312,16 +27443,30 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2026144308</v>
+      </c>
+      <c r="E35" s="15">
+        <v>46281</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>1227</v>
+      </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="20"/>
+      <c r="H35" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>1226</v>
+      </c>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27329,16 +27474,30 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2026144323</v>
+      </c>
+      <c r="E36" s="15">
+        <v>46281</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>1230</v>
+      </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="20"/>
+      <c r="H36" s="18" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>1229</v>
+      </c>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27346,16 +27505,30 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2026144324</v>
+      </c>
+      <c r="E37" s="15">
+        <v>46281</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>1233</v>
+      </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="20"/>
+      <c r="H37" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>1232</v>
+      </c>
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27363,16 +27536,30 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2026143434</v>
+      </c>
+      <c r="E38" s="15">
+        <v>46284</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>1236</v>
+      </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
-      <c r="H38" s="18"/>
-      <c r="I38" s="20"/>
+      <c r="H38" s="18" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>1235</v>
+      </c>
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -27380,16 +27567,30 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="16"/>
+      <c r="B39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="13">
+        <v>2026144322</v>
+      </c>
+      <c r="E39" s="15">
+        <v>46284</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>1239</v>
+      </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="18"/>
-      <c r="I39" s="20"/>
+      <c r="H39" s="18" t="s">
+        <v>1237</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>1238</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -28613,9 +28814,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I30">
-    <sortCondition ref="E7:E30"/>
-    <sortCondition ref="D7:D30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I39">
+    <sortCondition ref="E7:E39"/>
+    <sortCondition ref="D7:D39"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB8B6FA-CB46-4E6B-BE6E-1CE0477ABC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5B6036-5531-4F1F-A090-B6D1F23411FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="1289">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3983,6 +3983,153 @@
   </si>
   <si>
     <t>NB(425/2025)</t>
+  </si>
+  <si>
+    <t>NB(301/2026)</t>
+  </si>
+  <si>
+    <t>Mennad fatma</t>
+  </si>
+  <si>
+    <t>diar el chems</t>
+  </si>
+  <si>
+    <t>NB(407/2026)</t>
+  </si>
+  <si>
+    <t>Ouabel sebti</t>
+  </si>
+  <si>
+    <t>NB(346/2026)</t>
+  </si>
+  <si>
+    <t>Larouci dilmi</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 03 n 17</t>
+  </si>
+  <si>
+    <t>Ladek zoheir</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 14 n 20</t>
+  </si>
+  <si>
+    <t>NB(449/2026)</t>
+  </si>
+  <si>
+    <t>NB(418/2026)</t>
+  </si>
+  <si>
+    <t>Mag toumi mourad</t>
+  </si>
+  <si>
+    <t>draa essouk</t>
+  </si>
+  <si>
+    <t>Mag toumi khaled</t>
+  </si>
+  <si>
+    <t>Cheraout ali</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 18 n 09</t>
+  </si>
+  <si>
+    <t>NB(428/2026)</t>
+  </si>
+  <si>
+    <t>Tabani haçene</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 02 n 16</t>
+  </si>
+  <si>
+    <t>NB(447/2026)</t>
+  </si>
+  <si>
+    <t>Rabahi sidhoum djamel</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 13 n 07</t>
+  </si>
+  <si>
+    <t>NB(529/2025)</t>
+  </si>
+  <si>
+    <t>NB(465/2026)</t>
+  </si>
+  <si>
+    <t>Malki tahar</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 10 n 21</t>
+  </si>
+  <si>
+    <t>Guernouz med</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 1 n 3</t>
+  </si>
+  <si>
+    <t>NB(460/2026)</t>
+  </si>
+  <si>
+    <t>Baghdadi merouane</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 12 n 25</t>
+  </si>
+  <si>
+    <t>NB(452/2026)</t>
+  </si>
+  <si>
+    <t>Benaichouba med boubakeur</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 14 n 15</t>
+  </si>
+  <si>
+    <t>NB(453/2026)</t>
+  </si>
+  <si>
+    <t>Ferrah mustapha</t>
+  </si>
+  <si>
+    <t>cité 400 aadl bt 38 n 22</t>
+  </si>
+  <si>
+    <t>NB(184/2024)</t>
+  </si>
+  <si>
+    <t>NB(444/2026)</t>
+  </si>
+  <si>
+    <t>Benoua yahia</t>
+  </si>
+  <si>
+    <t>rue zouaoui ben kouider</t>
+  </si>
+  <si>
+    <t>Nabi rabia</t>
+  </si>
+  <si>
+    <t>NB(311/2026)</t>
+  </si>
+  <si>
+    <t>Mag hazene med</t>
+  </si>
+  <si>
+    <t>Khaladi f/zohra</t>
+  </si>
+  <si>
+    <t>NB(349/2026)</t>
+  </si>
+  <si>
+    <t>Khaladi sid ali</t>
+  </si>
+  <si>
+    <t>NB(348/2026)</t>
   </si>
 </sst>
 </file>
@@ -26527,7 +26674,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -26567,7 +26714,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>33</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -27597,304 +27744,570 @@
         <f>+A39+1</f>
         <v>34</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2026003591</v>
+      </c>
+      <c r="E40" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>1251</v>
+      </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="18"/>
-      <c r="I40" s="20"/>
+      <c r="H40" s="18" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>1253</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="16"/>
+      <c r="B41" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2026003596</v>
+      </c>
+      <c r="E41" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>1243</v>
+      </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="20"/>
+      <c r="H41" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="16"/>
+      <c r="B42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2026003600</v>
+      </c>
+      <c r="E42" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>1240</v>
+      </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="20"/>
+      <c r="H42" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="16"/>
+      <c r="B43" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2026003633</v>
+      </c>
+      <c r="E43" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>1251</v>
+      </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
-      <c r="H43" s="18"/>
-      <c r="I43" s="20"/>
+      <c r="H43" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>1253</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="16"/>
+      <c r="B44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="13">
+        <v>2026144321</v>
+      </c>
+      <c r="E44" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>1245</v>
+      </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
-      <c r="H44" s="18"/>
-      <c r="I44" s="20"/>
+      <c r="H44" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="16"/>
+      <c r="B45" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="13">
+        <v>2026144325</v>
+      </c>
+      <c r="E45" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>1250</v>
+      </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
-      <c r="H45" s="4"/>
-      <c r="I45" s="20"/>
+      <c r="H45" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>1249</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="16"/>
+      <c r="B46" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2026144327</v>
+      </c>
+      <c r="E46" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>1263</v>
+      </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
-      <c r="H46" s="18"/>
-      <c r="I46" s="20"/>
+      <c r="H46" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>1262</v>
+      </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="16"/>
+      <c r="B47" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="13">
+        <v>2026144329</v>
+      </c>
+      <c r="E47" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>1257</v>
+      </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
-      <c r="H47" s="18"/>
-      <c r="I47" s="20"/>
+      <c r="H47" s="18" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16"/>
+      <c r="B48" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="13">
+        <v>2026144330</v>
+      </c>
+      <c r="E48" s="15">
+        <v>46288</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>1260</v>
+      </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
-      <c r="H48" s="4"/>
-      <c r="I48" s="20"/>
+      <c r="H48" s="18" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I48" s="20" t="s">
+        <v>1259</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
+      <c r="B49" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" s="13">
+        <v>2026003598</v>
+      </c>
+      <c r="E49" s="15">
+        <v>46291</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>869</v>
+      </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4"/>
-      <c r="I49" s="20"/>
+      <c r="H49" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="I49" s="20" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
+      <c r="B50" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D50" s="13">
+        <v>2026003631</v>
+      </c>
+      <c r="E50" s="15">
+        <v>46294</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>1279</v>
+      </c>
       <c r="G50" s="17">
         <v>1</v>
       </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="20"/>
+      <c r="H50" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>1281</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="16"/>
+      <c r="B51" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="13">
+        <v>2026143440</v>
+      </c>
+      <c r="E51" s="15">
+        <v>46294</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>1275</v>
+      </c>
       <c r="G51" s="17">
         <v>1</v>
       </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="20"/>
+      <c r="H51" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I51" s="20" t="s">
+        <v>1274</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="16"/>
+      <c r="B52" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="13">
+        <v>2026143569</v>
+      </c>
+      <c r="E52" s="15">
+        <v>46294</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>1278</v>
+      </c>
       <c r="G52" s="17">
         <v>1</v>
       </c>
-      <c r="H52" s="4"/>
-      <c r="I52" s="20"/>
+      <c r="H52" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I52" s="20" t="s">
+        <v>1277</v>
+      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="16"/>
+      <c r="B53" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="13">
+        <v>2026143570</v>
+      </c>
+      <c r="E53" s="15">
+        <v>46294</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>1264</v>
+      </c>
       <c r="G53" s="17">
         <v>1</v>
       </c>
-      <c r="H53" s="4"/>
-      <c r="I53" s="20"/>
+      <c r="H53" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I53" s="20" t="s">
+        <v>1266</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="16"/>
+      <c r="B54" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="13">
+        <v>2026144326</v>
+      </c>
+      <c r="E54" s="15">
+        <v>46294</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>1269</v>
+      </c>
       <c r="G54" s="17">
         <v>1</v>
       </c>
-      <c r="H54" s="4"/>
-      <c r="I54" s="20"/>
+      <c r="H54" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I54" s="20" t="s">
+        <v>1268</v>
+      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="16"/>
+      <c r="B55" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="13">
+        <v>2026144328</v>
+      </c>
+      <c r="E55" s="15">
+        <v>46294</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>1272</v>
+      </c>
       <c r="G55" s="17">
         <v>1</v>
       </c>
-      <c r="H55" s="4"/>
-      <c r="I55" s="20"/>
+      <c r="H55" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I55" s="20" t="s">
+        <v>1271</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="16"/>
+      <c r="B56" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D56" s="13">
+        <v>2026003637</v>
+      </c>
+      <c r="E56" s="15">
+        <v>46295</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>1288</v>
+      </c>
       <c r="G56" s="17">
         <v>1</v>
       </c>
-      <c r="H56" s="4"/>
-      <c r="I56" s="20"/>
+      <c r="H56" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="I56" s="20" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="16"/>
+      <c r="B57" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D57" s="13">
+        <v>2026003638</v>
+      </c>
+      <c r="E57" s="15">
+        <v>46295</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>1286</v>
+      </c>
       <c r="G57" s="17">
         <v>1</v>
       </c>
-      <c r="H57" s="4"/>
-      <c r="I57" s="20"/>
+      <c r="H57" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="I57" s="20" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="16"/>
+      <c r="B58" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D58" s="13">
+        <v>2026003639</v>
+      </c>
+      <c r="E58" s="15">
+        <v>46295</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>1283</v>
+      </c>
       <c r="G58" s="17">
         <v>1</v>
       </c>
-      <c r="H58" s="4"/>
-      <c r="I58" s="20"/>
+      <c r="H58" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="I58" s="20" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
@@ -28814,9 +29227,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I39">
-    <sortCondition ref="E7:E39"/>
-    <sortCondition ref="D7:D39"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I58">
+    <sortCondition ref="E7:E58"/>
+    <sortCondition ref="D7:D58"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5B6036-5531-4F1F-A090-B6D1F23411FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634056C1-06CF-4356-B9EC-3BF57703DB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,15 +4992,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>104785</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>19060</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5015,8 +5015,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="695335" y="21678900"/>
-          <a:ext cx="4648190" cy="238125"/>
+          <a:off x="609610" y="11229975"/>
+          <a:ext cx="4629140" cy="5305425"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -27804,29 +27804,29 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B42" s="13" t="s">
-        <v>19</v>
+      <c r="B42" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D42" s="13">
-        <v>2026003600</v>
+        <v>2026003598</v>
       </c>
       <c r="E42" s="15">
         <v>46288</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>1240</v>
+        <v>869</v>
       </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
-      <c r="H42" s="18" t="s">
-        <v>1241</v>
+      <c r="H42" s="4" t="s">
+        <v>1282</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>1242</v>
+        <v>950</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -27835,28 +27835,28 @@
         <v>37</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D43" s="13">
-        <v>2026003633</v>
+        <v>2026003600</v>
       </c>
       <c r="E43" s="15">
         <v>46288</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>1251</v>
+        <v>1240</v>
       </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
-      <c r="H43" s="4" t="s">
-        <v>1254</v>
+      <c r="H43" s="18" t="s">
+        <v>1241</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>1253</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -27865,28 +27865,28 @@
         <v>38</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>18</v>
+        <v>284</v>
       </c>
       <c r="D44" s="13">
-        <v>2026144321</v>
+        <v>2026003633</v>
       </c>
       <c r="E44" s="15">
         <v>46288</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -27901,22 +27901,22 @@
         <v>18</v>
       </c>
       <c r="D45" s="13">
-        <v>2026144325</v>
+        <v>2026144321</v>
       </c>
       <c r="E45" s="15">
         <v>46288</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -27931,22 +27931,22 @@
         <v>18</v>
       </c>
       <c r="D46" s="13">
-        <v>2026144327</v>
+        <v>2026144325</v>
       </c>
       <c r="E46" s="15">
         <v>46288</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>1261</v>
+        <v>1248</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>1262</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27961,22 +27961,22 @@
         <v>18</v>
       </c>
       <c r="D47" s="13">
-        <v>2026144329</v>
+        <v>2026144327</v>
       </c>
       <c r="E47" s="15">
         <v>46288</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
-      <c r="H47" s="18" t="s">
-        <v>1255</v>
+      <c r="H47" s="4" t="s">
+        <v>1261</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -27991,22 +27991,22 @@
         <v>18</v>
       </c>
       <c r="D48" s="13">
-        <v>2026144330</v>
+        <v>2026144329</v>
       </c>
       <c r="E48" s="15">
         <v>46288</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="I48" s="20" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -28014,29 +28014,29 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="15" t="s">
-        <v>93</v>
+      <c r="B49" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="D49" s="13">
-        <v>2026003598</v>
+        <v>2026144330</v>
       </c>
       <c r="E49" s="15">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>869</v>
+        <v>1260</v>
       </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>1282</v>
+      <c r="H49" s="18" t="s">
+        <v>1258</v>
       </c>
       <c r="I49" s="20" t="s">
-        <v>950</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634056C1-06CF-4356-B9EC-3BF57703DB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD74975-46EA-4F04-A8C4-BE9C20A0D787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Juillet 2026" sheetId="7" r:id="rId7"/>
     <sheet name="Aout 2026" sheetId="8" r:id="rId8"/>
     <sheet name="Septembre 2026" sheetId="9" r:id="rId9"/>
+    <sheet name="Octobre 2026" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Aout 2026'!$1:$6</definedName>
@@ -32,6 +33,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Juin 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mai 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mars 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Octobre 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Septembre 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="1309">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -4130,6 +4132,66 @@
   </si>
   <si>
     <t>NB(348/2026)</t>
+  </si>
+  <si>
+    <t>BC0311</t>
+  </si>
+  <si>
+    <t>B21990</t>
+  </si>
+  <si>
+    <t>NB(469/2026)</t>
+  </si>
+  <si>
+    <t>Yagoub hafidha</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 10 n 11</t>
+  </si>
+  <si>
+    <t>Laidani sihem</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 06 n 30</t>
+  </si>
+  <si>
+    <t>NB(466/2026)</t>
+  </si>
+  <si>
+    <t>Omari wahid</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 16 n 14</t>
+  </si>
+  <si>
+    <t>NB(474/2026)</t>
+  </si>
+  <si>
+    <t>NB(333/2026)</t>
+  </si>
+  <si>
+    <t>Zaouidi djaber</t>
+  </si>
+  <si>
+    <t>Quartier chorfa</t>
+  </si>
+  <si>
+    <t>NB(445/2026)</t>
+  </si>
+  <si>
+    <t>Ent etb hadj mostfai</t>
+  </si>
+  <si>
+    <t>1er nov route n01</t>
+  </si>
+  <si>
+    <t>NB(446/2026)</t>
+  </si>
+  <si>
+    <t>Talbi bendaoud</t>
+  </si>
+  <si>
+    <t>oued guelete</t>
   </si>
 </sst>
 </file>
@@ -4427,6 +4489,61 @@
         <a:xfrm flipH="1">
           <a:off x="590550" y="19659600"/>
           <a:ext cx="4448175" cy="2609850"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19060</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3A58DBE-64B1-46E0-AE45-C30A57C33635}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609610" y="11229975"/>
+          <a:ext cx="4629140" cy="5305425"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -8300,6 +8417,2068 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D453316-6A86-4601-9B98-C5B6D51D3A29}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D7" s="13">
+        <v>2026003636</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46301</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="13">
+        <v>2026143436</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46301</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2026003384</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46302</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>1305</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2026003387</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46302</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>1307</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2026003388</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46302</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>1302</v>
+      </c>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2026143562</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46302</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2026143563</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46302</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2026143568</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46302</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>1292</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="18"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="18"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="18"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="20"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="18"/>
+      <c r="I48" s="20"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="18"/>
+      <c r="I49" s="20"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="20"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="20"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="20"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="20"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="20"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="20"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="20"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="20"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="20"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="20"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="20"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="20"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+      <c r="I62" s="20"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64" s="20"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="20"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="20"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="20"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" ref="A72:A117" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="20"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+      <c r="I74" s="20"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="20"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+      <c r="I76" s="20"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+      <c r="I77" s="20"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+      <c r="I78" s="20"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+      <c r="I79" s="20"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+      <c r="I80" s="20"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+      <c r="I81" s="20"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+      <c r="I82" s="20"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+      <c r="I83" s="20"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+      <c r="I84" s="20"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+      <c r="I85" s="20"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+      <c r="I86" s="20"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+      <c r="I87" s="20"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+      <c r="I89" s="20"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+      <c r="I90" s="20"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+      <c r="I91" s="20"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I14">
+    <sortCondition ref="E7:E14"/>
+    <sortCondition ref="D7:D14"/>
+  </sortState>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil1"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD74975-46EA-4F04-A8C4-BE9C20A0D787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C76F08-03A4-4733-9A33-DB99215C0A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="1322">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -4192,6 +4192,45 @@
   </si>
   <si>
     <t>oued guelete</t>
+  </si>
+  <si>
+    <t>NB(491/2026)</t>
+  </si>
+  <si>
+    <t>Harbi mebarek</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 1 n 12</t>
+  </si>
+  <si>
+    <t>Bensaad assia</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 13 n 12</t>
+  </si>
+  <si>
+    <t>NB(246/2026)</t>
+  </si>
+  <si>
+    <t>Moulesmara kamel</t>
+  </si>
+  <si>
+    <t>NB(482/2026)</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 13 n 29</t>
+  </si>
+  <si>
+    <t>Lantri gouzeil</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 17 n 17</t>
+  </si>
+  <si>
+    <t>NB(483/2026)</t>
+  </si>
+  <si>
+    <t>BB0262</t>
   </si>
 </sst>
 </file>
@@ -8468,7 +8507,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -8490,7 +8529,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -8530,7 +8569,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8814,16 +8853,30 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
+      <c r="B15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2026144373</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46307</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>1314</v>
+      </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="20"/>
+      <c r="H15" s="18" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>1313</v>
+      </c>
       <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8831,16 +8884,30 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="16"/>
+      <c r="B16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2026144375</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46307</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>1309</v>
+      </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="20"/>
+      <c r="H16" s="18" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>1311</v>
+      </c>
       <c r="J16" s="20"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8848,16 +8915,30 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
+      <c r="B17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2026144378</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46307</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>1320</v>
+      </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="20"/>
+      <c r="H17" s="18" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>1319</v>
+      </c>
       <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8865,16 +8946,30 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2026144380</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46307</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>1316</v>
+      </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="20"/>
+      <c r="H18" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>1317</v>
+      </c>
       <c r="J18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8882,11 +8977,21 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
+      <c r="B19" s="13" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C19" s="13">
+        <v>100</v>
+      </c>
+      <c r="D19" s="13">
+        <v>23987143</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46307</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
@@ -10455,9 +10560,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I14">
-    <sortCondition ref="E7:E14"/>
-    <sortCondition ref="D7:D14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I18">
+    <sortCondition ref="E7:E18"/>
+    <sortCondition ref="D7:D18"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C76F08-03A4-4733-9A33-DB99215C0A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF402EF-62B7-4CE1-87B8-114BB085C7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="1322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="1327">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -4231,6 +4231,21 @@
   </si>
   <si>
     <t>BB0262</t>
+  </si>
+  <si>
+    <t>B16515</t>
+  </si>
+  <si>
+    <t>NB(467/2026)</t>
+  </si>
+  <si>
+    <t>Epe latraco</t>
+  </si>
+  <si>
+    <t>diar echems</t>
+  </si>
+  <si>
+    <t>B11760</t>
   </si>
 </sst>
 </file>
@@ -8507,7 +8522,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -8529,7 +8544,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -8569,7 +8584,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8854,29 +8869,25 @@
         <v>9</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>18</v>
+        <v>1321</v>
+      </c>
+      <c r="C15" s="13">
+        <v>100</v>
       </c>
       <c r="D15" s="13">
-        <v>2026144373</v>
+        <v>23987143</v>
       </c>
       <c r="E15" s="15">
         <v>46307</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>1314</v>
+        <v>162</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
-      <c r="H15" s="18" t="s">
-        <v>1312</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>1313</v>
-      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="20"/>
       <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8891,22 +8902,22 @@
         <v>18</v>
       </c>
       <c r="D16" s="13">
-        <v>2026144375</v>
+        <v>2026144373</v>
       </c>
       <c r="E16" s="15">
         <v>46307</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="J16" s="20"/>
     </row>
@@ -8922,22 +8933,22 @@
         <v>18</v>
       </c>
       <c r="D17" s="13">
-        <v>2026144378</v>
+        <v>2026144375</v>
       </c>
       <c r="E17" s="15">
         <v>46307</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>1320</v>
+        <v>1309</v>
       </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="J17" s="20"/>
     </row>
@@ -8953,22 +8964,22 @@
         <v>18</v>
       </c>
       <c r="D18" s="13">
-        <v>2026144380</v>
+        <v>2026144378</v>
       </c>
       <c r="E18" s="15">
         <v>46307</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>1315</v>
+      <c r="H18" s="18" t="s">
+        <v>1318</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="J18" s="20"/>
     </row>
@@ -8978,25 +8989,29 @@
         <v>13</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C19" s="13">
-        <v>100</v>
+        <v>19</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="D19" s="13">
-        <v>23987143</v>
+        <v>2026144380</v>
       </c>
       <c r="E19" s="15">
         <v>46307</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>162</v>
+        <v>1316</v>
       </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="20"/>
+      <c r="H19" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>1317</v>
+      </c>
       <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9004,16 +9019,30 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2026003389</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46308</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>1323</v>
+      </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="20"/>
+      <c r="H20" s="18" t="s">
+        <v>1324</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>1325</v>
+      </c>
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9021,15 +9050,25 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="13" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2026143564</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46308</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
-      <c r="H21" s="18"/>
+      <c r="H21" s="4"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
@@ -9038,15 +9077,25 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
+      <c r="B22" s="13" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2026144372</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46308</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
@@ -10560,9 +10609,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I18">
-    <sortCondition ref="E7:E18"/>
-    <sortCondition ref="D7:D18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I22">
+    <sortCondition ref="E7:E22"/>
+    <sortCondition ref="D7:D22"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF402EF-62B7-4CE1-87B8-114BB085C7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67291130-B11B-4D86-8DEB-F7D5A14D4A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="1327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="1339">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -4246,6 +4246,42 @@
   </si>
   <si>
     <t>B11760</t>
+  </si>
+  <si>
+    <t>B22444</t>
+  </si>
+  <si>
+    <t>B12249</t>
+  </si>
+  <si>
+    <t>NB(342/2026)</t>
+  </si>
+  <si>
+    <t>Temmar miloud</t>
+  </si>
+  <si>
+    <t>residence chorfi bloc a</t>
+  </si>
+  <si>
+    <t>NB(473/2026)</t>
+  </si>
+  <si>
+    <t>Berber nadji</t>
+  </si>
+  <si>
+    <t>oued el monchar</t>
+  </si>
+  <si>
+    <t>B10343</t>
+  </si>
+  <si>
+    <t>BC0562</t>
+  </si>
+  <si>
+    <t>BC0011</t>
+  </si>
+  <si>
+    <t>BC0010</t>
   </si>
 </sst>
 </file>
@@ -8522,7 +8558,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -8544,7 +8580,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -8584,7 +8620,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -9104,11 +9140,21 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
+      <c r="B23" s="13" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2026143413</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46312</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
@@ -9121,11 +9167,21 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="13" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2026144376</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46312</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
@@ -9138,15 +9194,25 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="13" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2026003431</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46313</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="18"/>
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
@@ -9155,16 +9221,30 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2026003432</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46313</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>1332</v>
+      </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="20"/>
+      <c r="H26" s="18" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>1334</v>
+      </c>
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9172,15 +9252,25 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="13" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2026003438</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46313</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
-      <c r="H27" s="4"/>
+      <c r="H27" s="18"/>
       <c r="I27" s="20"/>
       <c r="J27" s="20"/>
     </row>
@@ -9189,16 +9279,30 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2026143411</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46313</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>1329</v>
+      </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="20"/>
+      <c r="H28" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>1331</v>
+      </c>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9206,11 +9310,21 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="13" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2026143412</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46313</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
@@ -9223,15 +9337,25 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="13" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2026143414</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46313</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H30" s="18"/>
+      <c r="H30" s="4"/>
       <c r="I30" s="20"/>
       <c r="J30" s="4"/>
     </row>
@@ -10609,9 +10733,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I22">
-    <sortCondition ref="E7:E22"/>
-    <sortCondition ref="D7:D22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I30">
+    <sortCondition ref="E7:E30"/>
+    <sortCondition ref="D7:D30"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67291130-B11B-4D86-8DEB-F7D5A14D4A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B49B5CE-76C0-4707-890E-D8EE39FB7ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="1345">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -4282,6 +4282,24 @@
   </si>
   <si>
     <t>BC0010</t>
+  </si>
+  <si>
+    <t>NB(488/2026)</t>
+  </si>
+  <si>
+    <t>Boutaleb abderzaq</t>
+  </si>
+  <si>
+    <t>cité 720 logts bt 19 n 22</t>
+  </si>
+  <si>
+    <t>NB(005/2022)</t>
+  </si>
+  <si>
+    <t>Benaissa a/cherif</t>
+  </si>
+  <si>
+    <t>B30181</t>
   </si>
 </sst>
 </file>
@@ -8558,7 +8576,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -8580,7 +8598,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -8620,7 +8638,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -9364,16 +9382,30 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2026144374</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46313</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>1339</v>
+      </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="20"/>
+      <c r="H31" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>1341</v>
+      </c>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9381,15 +9413,25 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="B32" s="13" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2026143418</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46316</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
-      <c r="H32" s="18"/>
+      <c r="H32" s="4"/>
       <c r="I32" s="20"/>
       <c r="J32" s="4"/>
     </row>
@@ -9398,16 +9440,30 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2026143420</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46316</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>1342</v>
+      </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="20"/>
+      <c r="H33" s="18" t="s">
+        <v>1343</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>1253</v>
+      </c>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10733,9 +10789,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I30">
-    <sortCondition ref="E7:E30"/>
-    <sortCondition ref="D7:D30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I33">
+    <sortCondition ref="E7:E33"/>
+    <sortCondition ref="D7:D33"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B49B5CE-76C0-4707-890E-D8EE39FB7ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9CFDF9-540E-4784-8C0D-ACF853FDF7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="1345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1349">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -4300,6 +4300,18 @@
   </si>
   <si>
     <t>B30181</t>
+  </si>
+  <si>
+    <t>NB(475/2026)</t>
+  </si>
+  <si>
+    <t>Hassam samir</t>
+  </si>
+  <si>
+    <t>villa z'hun n 54</t>
+  </si>
+  <si>
+    <t>B21195</t>
   </si>
 </sst>
 </file>
@@ -8576,7 +8588,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -8598,7 +8610,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -8638,7 +8650,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -9471,16 +9483,30 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2026003437</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46320</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>1345</v>
+      </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="20"/>
+      <c r="H34" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>1347</v>
+      </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9488,11 +9514,21 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="13" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2026143417</v>
+      </c>
+      <c r="E35" s="15">
+        <v>46321</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
